--- a/data/reference_rates_master.xlsx
+++ b/data/reference_rates_master.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="H2" s="9" t="n">
-        <v>46242.81875346065</v>
+        <v>46242.83060650463</v>
       </c>
     </row>
     <row r="3">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="H3" s="9" t="n">
-        <v>46242.81875609954</v>
+        <v>46242.83060659722</v>
       </c>
     </row>
     <row r="4">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="H4" s="9" t="n">
-        <v>46242.81875914352</v>
+        <v>46242.83060667824</v>
       </c>
     </row>
     <row r="5">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="H5" s="9" t="n">
-        <v>46242.81875077546</v>
+        <v>46242.83060642361</v>
       </c>
     </row>
   </sheetData>
